--- a/data/records.xlsx
+++ b/data/records.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="161">
   <si>
     <t xml:space="preserve">category</t>
   </si>
@@ -2501,8 +2501,8 @@
       <c r="E67" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F67" s="1" t="n">
-        <v>43.8</v>
+      <c r="F67" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
